--- a/AAII_Financials/Quarterly/KIND_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KIND_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
   <si>
     <t>KIND</t>
   </si>
@@ -656,113 +656,116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>55600</v>
+      </c>
+      <c r="E8" s="3">
         <v>56100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>56900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>49800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>53300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>54000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>54500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>51000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>192200</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -778,19 +781,22 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E9" s="3">
         <v>10700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10400</v>
-      </c>
-      <c r="F9" s="3">
-        <v>9900</v>
       </c>
       <c r="G9" s="3">
         <v>9900</v>
@@ -799,17 +805,17 @@
         <v>9900</v>
       </c>
       <c r="I9" s="3">
+        <v>9900</v>
+      </c>
+      <c r="J9" s="3">
         <v>10200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>28800</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -825,38 +831,41 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>45100</v>
+      </c>
+      <c r="E10" s="3">
         <v>45400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>46500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>39900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>43400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>44100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>44300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>41900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>163400</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -872,8 +881,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,38 +903,39 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E12" s="3">
         <v>39600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>37100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>33000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>32000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>33400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>32700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>29000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>97100</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -938,8 +951,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,31 +1001,34 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>11100</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1032,8 +1051,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1079,8 +1101,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,85 +1120,89 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E17" s="3">
         <v>100500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>98300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>88600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>89600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>90300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>92800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>84200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>284300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>100</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-47600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-44400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-41400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-38800</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-36300</v>
       </c>
       <c r="H18" s="3">
         <v>-36300</v>
       </c>
       <c r="I18" s="3">
+        <v>-36300</v>
+      </c>
+      <c r="J18" s="3">
         <v>-38300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-33200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-92100</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1189,8 +1218,11 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1208,38 +1240,39 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E20" s="3">
         <v>6500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>6200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>9900</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1255,38 +1288,41 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-39100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-36400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-33800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-32000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-30600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-32900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-35400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-31600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-78100</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1302,8 +1338,11 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1349,85 +1388,91 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-40500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-37800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-35300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-33400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-32100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-34400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-36800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-32900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-82200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-13700</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1443,8 +1488,11 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,102 +1538,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-40500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-38100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-35400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-33700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-33400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-34700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-36800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-32900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-82400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13700</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-40500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-38100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-35400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-33700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-33400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-34700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-36800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-32900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-82400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13700</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,8 +1688,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1678,8 +1738,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1788,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,38 +1838,41 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-6200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-9900</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1819,55 +1888,61 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-40500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-38100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-35400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-33700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-33400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-34700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-36800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-32900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-82400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-13700</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,107 +1988,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-40500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-38100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-35400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-33700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-33400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-34700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-36800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-32900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-82400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-13700</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2115,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,85 +2135,89 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E41" s="3">
         <v>48400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>74300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>67800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>55200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>90700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>40200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>208000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>521800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1700</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>470900</v>
+      </c>
+      <c r="E42" s="3">
         <v>491300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>477300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>507000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>528100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>513700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>626100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>503900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>194000</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2144,38 +2233,41 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E43" s="3">
         <v>30000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>28400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>28000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>29800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>27000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>26200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>22100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>29700</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2191,8 +2283,11 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2238,102 +2333,111 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E45" s="3">
         <v>11100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>11200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>27200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16300</v>
-      </c>
-      <c r="L45" s="3">
-        <v>700</v>
       </c>
       <c r="M45" s="3">
         <v>700</v>
       </c>
       <c r="N45" s="3">
+        <v>700</v>
+      </c>
+      <c r="O45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>566900</v>
+      </c>
+      <c r="E46" s="3">
         <v>580800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>592100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>614100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>625300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>641700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>719700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>745700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>761700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2300</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2364,53 +2468,56 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N47" s="3">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3">
         <v>416300</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E48" s="3">
         <v>67200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>69200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>71200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>64400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>66900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>68100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>70600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>72000</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2426,38 +2533,41 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E49" s="3">
         <v>3000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6000</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2473,8 +2583,11 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2633,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,28 +2683,31 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E52" s="3">
         <v>19200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>19400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>600</v>
-      </c>
-      <c r="I52" s="3">
-        <v>300</v>
       </c>
       <c r="J52" s="3">
         <v>300</v>
@@ -2597,25 +2716,28 @@
         <v>300</v>
       </c>
       <c r="L52" s="3">
+        <v>300</v>
+      </c>
+      <c r="M52" s="3">
         <v>416700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>416800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>700</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,55 +2783,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>654600</v>
+      </c>
+      <c r="E54" s="3">
         <v>670100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>684000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>694800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>699600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>713900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>793200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>822200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>840100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>417900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>418500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>419300</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2855,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,55 +2875,59 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E57" s="3">
         <v>3300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6200</v>
-      </c>
-      <c r="L57" s="3">
-        <v>100</v>
       </c>
       <c r="M57" s="3">
         <v>100</v>
       </c>
       <c r="N57" s="3">
+        <v>100</v>
+      </c>
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2840,102 +2973,111 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E59" s="3">
         <v>31300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>31100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>28200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>30100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>28200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>28600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>31300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>27300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>200</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E60" s="3">
         <v>34600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>37100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>33200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>34700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>34600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>34800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>33500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>700</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2981,55 +3123,61 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E62" s="3">
         <v>62300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>63900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>65100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>53800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>55800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>57800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>59700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>61600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>24900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>31100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14600</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3223,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3273,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,55 +3323,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E66" s="3">
         <v>96900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>101000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>98400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>88500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>90500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>91700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>94500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>95100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>26700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>31300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15300</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3395,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3443,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3493,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3376,8 +3543,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,55 +3593,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-766000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-725500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-687400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-652000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-618300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-584800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-550100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-513300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-480300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-25200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-29200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-100</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3693,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3743,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,55 +3793,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>558600</v>
+      </c>
+      <c r="E76" s="3">
         <v>573200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>583100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>596400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>611100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>623500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>701500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>727700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>745000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>391200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>387200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>404000</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,107 +3893,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-40500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-38100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-35400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-33700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-33400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-34700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-36800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-32900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-82400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-13700</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,13 +4020,14 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="E83" s="3">
         <v>1500</v>
@@ -3844,34 +4042,37 @@
         <v>1500</v>
       </c>
       <c r="I83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J83" s="3">
         <v>1400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1300</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
         <v>1100</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4118,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4168,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4218,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4268,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,55 +4318,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-18300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-12300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-19700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-12700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-22600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-49500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-800</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,13 +4390,14 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
@@ -4186,40 +4406,43 @@
         <v>-100</v>
       </c>
       <c r="G91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3">
         <v>-1900</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4488,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,55 +4538,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>28000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>24700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-17000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>110200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-124100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-311500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>266800</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-425300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>9000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,8 +4610,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4425,8 +4658,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4708,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4758,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,55 +4808,61 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>500</v>
+      </c>
+      <c r="E100" s="3">
         <v>4800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-47300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-21500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>218900</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>418800</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4628,83 +4876,89 @@
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-25900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>17700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-35500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>50500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-167800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-313800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>436500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5200</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KIND_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KIND_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
   <si>
     <t>KIND</t>
   </si>
@@ -656,119 +656,123 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>53100</v>
+      </c>
+      <c r="E8" s="3">
         <v>55600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>56100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>56900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>49800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>53300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>54000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>54500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>51000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>192200</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -784,22 +788,25 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E9" s="3">
         <v>10500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10400</v>
-      </c>
-      <c r="G9" s="3">
-        <v>9900</v>
       </c>
       <c r="H9" s="3">
         <v>9900</v>
@@ -808,17 +815,17 @@
         <v>9900</v>
       </c>
       <c r="J9" s="3">
+        <v>9900</v>
+      </c>
+      <c r="K9" s="3">
         <v>10200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>28800</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -834,41 +841,44 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E10" s="3">
         <v>45100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>45400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>46500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>39900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>43400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>44100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>44300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>41900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>163400</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -884,8 +894,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,41 +917,42 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E12" s="3">
         <v>34200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>39600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>37100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>33000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>32000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>33400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>32700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>29000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>97100</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -954,8 +968,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1004,17 +1021,20 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>11100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1030,8 +1050,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1054,8 +1074,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1104,8 +1127,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1121,91 +1147,95 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>87900</v>
+      </c>
+      <c r="E17" s="3">
         <v>103200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>100500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>98300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>88600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>89600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>90300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>92800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>84200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>284300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>100</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-47600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-44400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-41400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-38800</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-36300</v>
       </c>
       <c r="I18" s="3">
         <v>-36300</v>
       </c>
       <c r="J18" s="3">
+        <v>-36300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-38300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-33200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-92100</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1221,8 +1251,11 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1241,41 +1274,42 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E20" s="3">
         <v>7100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>6500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>6200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>9900</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1291,41 +1325,44 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-39100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-36400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-33800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-32000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-30600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-32900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-35400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-31600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-78100</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1341,8 +1378,11 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1391,91 +1431,97 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-28100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-40500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-37800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-35300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-33400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-32100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-34400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-36800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-32900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-82200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-13700</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1491,8 +1537,11 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1541,108 +1590,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-40500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-38100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-35400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-33700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-33400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-34700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-36800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-32900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-82400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-13700</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-40500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-38100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-35400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-33700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-33400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-34700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-36800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-32900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-82400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-13700</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,8 +1749,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1741,8 +1802,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1791,8 +1855,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1841,41 +1908,44 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-6500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-6200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-9900</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1891,58 +1961,64 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-40500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-38100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-35400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-33700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-33400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-34700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-36800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-32900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-82400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-13700</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1991,113 +2067,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-40500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-38100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-35400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-33700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-33400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-34700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-36800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-32900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-82400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-13700</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2116,8 +2201,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2136,91 +2222,95 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>69700</v>
+      </c>
+      <c r="E41" s="3">
         <v>60200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>48400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>74300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>67800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>55200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>90700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>40200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>208000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>521800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1700</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>428100</v>
+      </c>
+      <c r="E42" s="3">
         <v>470900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>491300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>477300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>507000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>528100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>513700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>626100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>503900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>194000</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2236,41 +2326,44 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E43" s="3">
         <v>26200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>30000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>28400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>28000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>29800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>27000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>26200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>22100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>29700</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2286,8 +2379,11 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2336,108 +2432,117 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E45" s="3">
         <v>9600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>11100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>27200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>16300</v>
-      </c>
-      <c r="M45" s="3">
-        <v>700</v>
       </c>
       <c r="N45" s="3">
         <v>700</v>
       </c>
       <c r="O45" s="3">
+        <v>700</v>
+      </c>
+      <c r="P45" s="3">
         <v>600</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>540200</v>
+      </c>
+      <c r="E46" s="3">
         <v>566900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>580800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>592100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>614100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>625300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>641700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>719700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>745700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>761700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2300</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2471,56 +2576,59 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
         <v>416300</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E48" s="3">
         <v>65100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>67200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>69200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>71200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>64400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>66900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>68100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>70600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>72000</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2536,41 +2644,44 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E49" s="3">
         <v>2500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6000</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2586,8 +2697,11 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2636,8 +2750,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2686,31 +2803,34 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E52" s="3">
         <v>20100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>19200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>600</v>
-      </c>
-      <c r="J52" s="3">
-        <v>300</v>
       </c>
       <c r="K52" s="3">
         <v>300</v>
@@ -2719,25 +2839,28 @@
         <v>300</v>
       </c>
       <c r="M52" s="3">
+        <v>300</v>
+      </c>
+      <c r="N52" s="3">
         <v>416700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>416800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>700</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2786,58 +2909,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>633100</v>
+      </c>
+      <c r="E54" s="3">
         <v>654600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>670100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>684000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>694800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>699600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>713900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>793200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>822200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>840100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>417900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>418500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>419300</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2856,8 +2985,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2876,58 +3006,62 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6200</v>
-      </c>
-      <c r="M57" s="3">
-        <v>100</v>
       </c>
       <c r="N57" s="3">
         <v>100</v>
       </c>
       <c r="O57" s="3">
+        <v>100</v>
+      </c>
+      <c r="P57" s="3">
         <v>500</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2976,108 +3110,117 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E59" s="3">
         <v>33500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>31300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>31100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>28200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>30100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>28200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>28600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>31300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>27300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>200</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E60" s="3">
         <v>35400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>34600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>37100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>34700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>34600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>33900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>34800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>33500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>700</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3126,58 +3269,64 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E62" s="3">
         <v>60600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>62300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>63900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>65100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>53800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>55800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>57800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>59700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>61600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>24900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>31100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14600</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3226,8 +3375,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3276,8 +3428,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3326,58 +3481,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>91600</v>
+      </c>
+      <c r="E66" s="3">
         <v>96000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>96900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>101000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>98400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>88500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>90500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>91700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>94500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>95100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>26700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>31300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15300</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3396,8 +3557,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3446,8 +3608,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3496,8 +3661,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3546,8 +3714,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3596,58 +3767,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-794300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-766000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-725500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-687400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-652000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-618300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-584800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-550100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-513300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-480300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-25200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-29200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-100</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3696,8 +3873,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3746,8 +3926,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3796,58 +3979,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>541400</v>
+      </c>
+      <c r="E76" s="3">
         <v>558600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>573200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>583100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>596400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>611100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>623500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>701500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>727700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>745000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>391200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>387200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>404000</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3896,113 +4085,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-40500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-38100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-35400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-33700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-33400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-34700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-36800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-32900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-82400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-13700</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4021,8 +4219,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4030,7 +4229,7 @@
         <v>1400</v>
       </c>
       <c r="E83" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="F83" s="3">
         <v>1500</v>
@@ -4045,34 +4244,37 @@
         <v>1500</v>
       </c>
       <c r="J83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K83" s="3">
         <v>1400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1300</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
         <v>1100</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4121,8 +4323,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4171,8 +4376,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4221,8 +4429,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4271,8 +4482,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4321,58 +4535,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-14900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-18300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-12300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-19700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-12700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-22600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-49500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-800</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4391,8 +4611,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4400,7 +4621,7 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
@@ -4409,40 +4630,43 @@
         <v>-100</v>
       </c>
       <c r="H91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7000</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1900</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4491,8 +4715,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4541,58 +4768,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E94" s="3">
         <v>26300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-12400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>28000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>24700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>110200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-124100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-311500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>266800</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-425300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>9000</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4611,8 +4844,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4661,8 +4895,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4711,8 +4948,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4761,8 +5001,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4811,63 +5054,69 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E100" s="3">
         <v>500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-47300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-21500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>218900</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>418800</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
@@ -4879,86 +5128,92 @@
         <v>0</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E102" s="3">
         <v>11800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-25900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>17700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-35500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>50500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-167800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-313800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>436500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>5200</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KIND_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KIND_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
   <si>
     <t>KIND</t>
   </si>
@@ -656,126 +656,130 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>63300</v>
+      </c>
+      <c r="E8" s="3">
         <v>53100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>55600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>56100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>56900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>49800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>53300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>54000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>54500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>51000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>192200</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
@@ -791,25 +795,28 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E9" s="3">
         <v>10000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10400</v>
-      </c>
-      <c r="H9" s="3">
-        <v>9900</v>
       </c>
       <c r="I9" s="3">
         <v>9900</v>
@@ -818,17 +825,17 @@
         <v>9900</v>
       </c>
       <c r="K9" s="3">
+        <v>9900</v>
+      </c>
+      <c r="L9" s="3">
         <v>10200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>28800</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -844,44 +851,47 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E10" s="3">
         <v>43100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>45100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>45400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>46500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>39900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>43400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>44100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>44300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>41900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>163400</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -897,8 +907,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,44 +931,45 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E12" s="3">
         <v>31300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>34200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>39600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>37100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>33000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>32000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>33400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>32700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>29000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>97100</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
@@ -971,8 +985,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,20 +1041,23 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>11100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1053,8 +1073,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1077,8 +1097,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1130,8 +1153,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,97 +1174,101 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>112300</v>
+      </c>
+      <c r="E17" s="3">
         <v>87900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>103200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>100500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>98300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>88600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>89600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>90300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>92800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>84200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>284300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>100</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-34800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-47600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-44400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-41400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-38800</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-36300</v>
       </c>
       <c r="J18" s="3">
         <v>-36300</v>
       </c>
       <c r="K18" s="3">
+        <v>-36300</v>
+      </c>
+      <c r="L18" s="3">
         <v>-38300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-33200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-92100</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1254,8 +1284,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1275,44 +1308,45 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E20" s="3">
         <v>6700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>6500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>6200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>5400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>9900</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1328,44 +1362,47 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-41300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-26700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-39100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-36400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-33800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-32000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-30600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-32900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-35400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-31600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-78100</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1381,8 +1418,11 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1434,97 +1474,103 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-42500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-28100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-40500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-37800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-35300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-33400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-32100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-34400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-36800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-32900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-82200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1540,8 +1586,11 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,114 +1642,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-42800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-28300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-40500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-38100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-35400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-33700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-33400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-34700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-36800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-32900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-82400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-42800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-28300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-40500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-38100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-35400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-33700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-33400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-34700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-36800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-32900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-82400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1810,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1805,8 +1866,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1922,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,44 +1978,47 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-6500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-6200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-5400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-9900</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1964,61 +2034,67 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-42800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-28300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-40500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-38100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-35400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-33700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-33400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-34700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-36800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-32900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-82400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,119 +2146,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-42800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-28300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-40500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-38100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-35400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-33700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-33400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-34700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-36800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-32900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-82400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2287,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,97 +2309,101 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E41" s="3">
         <v>69700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>60200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>48400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>74300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>67800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>55200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>90700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>40200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>208000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>521800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1700</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>403600</v>
+      </c>
+      <c r="E42" s="3">
         <v>428100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>470900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>491300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>477300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>507000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>528100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>513700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>626100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>503900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>194000</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2329,44 +2419,47 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E43" s="3">
         <v>26100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>26200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>30000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>28400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>28000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>29800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>27000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>26200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>22100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>29700</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2382,8 +2475,11 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2435,114 +2531,123 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E45" s="3">
         <v>16400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>11100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>27200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16300</v>
-      </c>
-      <c r="N45" s="3">
-        <v>700</v>
       </c>
       <c r="O45" s="3">
         <v>700</v>
       </c>
       <c r="P45" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q45" s="3">
         <v>600</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>493200</v>
+      </c>
+      <c r="E46" s="3">
         <v>540200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>566900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>580800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>592100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>614100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>625300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>641700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>719700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>745700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>761700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2300</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2579,59 +2684,62 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
         <v>416300</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E48" s="3">
         <v>62900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>65100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>67200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>69200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>71200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>64400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>66900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>68100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>70600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>72000</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,44 +2755,47 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E49" s="3">
         <v>2100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6000</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,8 +2811,11 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2867,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,8 +2923,11 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2815,25 +2935,25 @@
         <v>27800</v>
       </c>
       <c r="E52" s="3">
+        <v>27800</v>
+      </c>
+      <c r="F52" s="3">
         <v>20100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>19400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>600</v>
-      </c>
-      <c r="K52" s="3">
-        <v>300</v>
       </c>
       <c r="L52" s="3">
         <v>300</v>
@@ -2842,25 +2962,28 @@
         <v>300</v>
       </c>
       <c r="N52" s="3">
+        <v>300</v>
+      </c>
+      <c r="O52" s="3">
         <v>416700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>416800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>700</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,61 +3035,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>542100</v>
+      </c>
+      <c r="E54" s="3">
         <v>633100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>654600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>670100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>684000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>694800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>699600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>713900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>793200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>822200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>840100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>417900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>418500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>419300</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3115,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,61 +3137,65 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E57" s="3">
         <v>2100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6200</v>
-      </c>
-      <c r="N57" s="3">
-        <v>100</v>
       </c>
       <c r="O57" s="3">
         <v>100</v>
       </c>
       <c r="P57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3113,61 +3247,67 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E59" s="3">
         <v>30600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>33500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>31300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>31100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>28200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>30100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>28200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>28600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>31300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>27300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>200</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3175,52 +3315,55 @@
         <v>32700</v>
       </c>
       <c r="E60" s="3">
+        <v>32700</v>
+      </c>
+      <c r="F60" s="3">
         <v>35400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>34600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>37100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>33200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>34700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>34600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>33900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>34800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>33500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>700</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3272,61 +3415,67 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E62" s="3">
         <v>58900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>60600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>62300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>63900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>65100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>53800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>55800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>57800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>59700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>61600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>24900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>31100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>14600</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3527,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3583,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,61 +3639,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>69800</v>
+      </c>
+      <c r="E66" s="3">
         <v>91600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>96000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>96900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>101000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>98400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>88500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>90500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>91700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>94500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>95100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>26700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>31300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15300</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3719,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3773,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3829,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3717,8 +3885,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,61 +3941,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-837100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-794300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-766000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-725500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-687400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-652000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-618300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-584800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-550100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-513300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-480300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-25200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-29200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-100</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4053,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4109,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,61 +4165,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>472300</v>
+      </c>
+      <c r="E76" s="3">
         <v>541400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>558600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>573200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>583100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>596400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>611100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>623500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>701500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>727700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>745000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>391200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>387200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>404000</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,119 +4277,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-42800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-28300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-40500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-38100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-35400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-33700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-33400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-34700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-36800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-32900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-82400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,19 +4418,20 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1400</v>
+        <v>1100</v>
       </c>
       <c r="E83" s="3">
         <v>1400</v>
       </c>
       <c r="F83" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="G83" s="3">
         <v>1500</v>
@@ -4247,34 +4446,37 @@
         <v>1500</v>
       </c>
       <c r="K83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L83" s="3">
         <v>1400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1300</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3">
         <v>1100</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4528,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4584,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4640,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4696,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,61 +4752,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-13600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-14900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-18300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-12300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-13700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-19700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-12700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-22600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-49500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-800</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,19 +4832,20 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
@@ -4633,40 +4854,43 @@
         <v>-100</v>
       </c>
       <c r="I91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7000</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +4942,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,61 +4998,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E94" s="3">
         <v>35900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>26300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>28000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>24700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-17000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>110200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-124100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-311500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>266800</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-425300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>9000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,8 +5078,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4898,8 +5132,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5188,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5244,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,70 +5300,76 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-36900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-12900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-47300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-21500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>218900</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>418800</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
@@ -5131,89 +5380,95 @@
         <v>0</v>
       </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E102" s="3">
         <v>9400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>11800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-25900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>17700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-35500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>50500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-167800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-313800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>436500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5200</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KIND_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KIND_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
   <si>
     <t>KIND</t>
   </si>
@@ -656,133 +656,137 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>65600</v>
+      </c>
+      <c r="E8" s="3">
         <v>63300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>53100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>55600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>56100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>56900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>49800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>53300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>54000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>54500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>51000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>192200</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -798,28 +802,31 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E9" s="3">
         <v>10300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10400</v>
-      </c>
-      <c r="I9" s="3">
-        <v>9900</v>
       </c>
       <c r="J9" s="3">
         <v>9900</v>
@@ -828,17 +835,17 @@
         <v>9900</v>
       </c>
       <c r="L9" s="3">
+        <v>9900</v>
+      </c>
+      <c r="M9" s="3">
         <v>10200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>28800</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -854,47 +861,50 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>54500</v>
+      </c>
+      <c r="E10" s="3">
         <v>53000</v>
       </c>
-      <c r="E10" s="3">
-        <v>43100</v>
-      </c>
       <c r="F10" s="3">
-        <v>45100</v>
+        <v>43200</v>
       </c>
       <c r="G10" s="3">
+        <v>45000</v>
+      </c>
+      <c r="H10" s="3">
         <v>45400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>46500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>39900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>43400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>44100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>44300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>41900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>163400</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -910,8 +920,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -932,47 +945,48 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E12" s="3">
         <v>31100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>31300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>34200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>39600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>37100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>33000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>32000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>33400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>32700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>29000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>97100</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
@@ -988,8 +1002,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1044,8 +1061,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1055,12 +1075,12 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>11100</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1076,8 +1096,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1100,31 +1120,34 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1156,8 +1179,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1175,103 +1201,107 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>86400</v>
+      </c>
+      <c r="E17" s="3">
         <v>112300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>87900</v>
       </c>
-      <c r="F17" s="3">
-        <v>103200</v>
-      </c>
       <c r="G17" s="3">
+        <v>92100</v>
+      </c>
+      <c r="H17" s="3">
         <v>100500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>98300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>88600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>89600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>90300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>92800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>84200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>284300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>100</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-20800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-49000</v>
       </c>
-      <c r="E18" s="3">
-        <v>-34800</v>
-      </c>
       <c r="F18" s="3">
-        <v>-47600</v>
+        <v>-34700</v>
       </c>
       <c r="G18" s="3">
+        <v>-36600</v>
+      </c>
+      <c r="H18" s="3">
         <v>-44400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-41400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-38800</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-36300</v>
       </c>
       <c r="K18" s="3">
         <v>-36300</v>
       </c>
       <c r="L18" s="3">
+        <v>-36300</v>
+      </c>
+      <c r="M18" s="3">
         <v>-38300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-33200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-92100</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1287,8 +1317,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1309,47 +1342,48 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>6500</v>
+        <v>-200</v>
       </c>
       <c r="E20" s="3">
-        <v>6700</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
-        <v>7100</v>
+        <v>200</v>
       </c>
       <c r="G20" s="3">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>6200</v>
+        <v>200</v>
       </c>
       <c r="I20" s="3">
-        <v>5400</v>
+        <v>200</v>
       </c>
       <c r="J20" s="3">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3">
         <v>4200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>9900</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1365,47 +1399,50 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-41300</v>
+        <v>-19800</v>
       </c>
       <c r="E21" s="3">
-        <v>-26700</v>
+        <v>-47700</v>
       </c>
       <c r="F21" s="3">
-        <v>-39100</v>
+        <v>-33500</v>
       </c>
       <c r="G21" s="3">
-        <v>-36400</v>
+        <v>-35100</v>
       </c>
       <c r="H21" s="3">
-        <v>-33800</v>
+        <v>-43100</v>
       </c>
       <c r="I21" s="3">
-        <v>-32000</v>
+        <v>-40200</v>
       </c>
       <c r="J21" s="3">
+        <v>-37500</v>
+      </c>
+      <c r="K21" s="3">
         <v>-30600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-32900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-35400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-31600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-78100</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1421,31 +1458,34 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1477,103 +1517,109 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-42500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-28100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-40500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-37800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-35300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-33400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-32100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-34400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-36800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-32900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-82200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-13700</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1589,8 +1635,11 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1645,120 +1694,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-42800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-28300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-40500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-38100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-35400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-33700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-33400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-34700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-36800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-32900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-82400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-13700</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-42800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-28300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-40500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-38100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-35400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-33700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-33400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-34700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-36800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-32900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-82400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-13700</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1813,8 +1871,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1869,8 +1930,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1925,8 +1989,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1981,47 +2048,50 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-6500</v>
+        <v>200</v>
       </c>
       <c r="E32" s="3">
-        <v>-6700</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
-        <v>-7100</v>
+        <v>-200</v>
       </c>
       <c r="G32" s="3">
-        <v>-6500</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-6200</v>
+        <v>-200</v>
       </c>
       <c r="I32" s="3">
-        <v>-5400</v>
+        <v>-200</v>
       </c>
       <c r="J32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-4200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-9900</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2037,64 +2107,70 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-42800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-28300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-40500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-38100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-35400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-33700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-33400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-34700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-36800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-32900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-82400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-13700</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2149,125 +2225,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-42800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-28300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-40500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-38100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-35400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-33700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-33400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-34700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-36800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-32900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-82400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-13700</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2288,8 +2373,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2310,103 +2396,107 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E41" s="3">
         <v>53000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>69700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>60200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>48400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>74300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>67800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>55200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>90700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>40200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>208000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>521800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1700</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>375000</v>
+      </c>
+      <c r="E42" s="3">
         <v>403600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>428100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>470900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>491300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>477300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>507000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>528100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>513700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>626100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>503900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>194000</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2422,47 +2512,50 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E43" s="3">
         <v>28100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>26100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>26200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>30000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>28400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>28000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>29800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>27000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>26200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>22100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>29700</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2478,31 +2571,34 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2534,143 +2630,152 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>8500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>16400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>9600</v>
-      </c>
-      <c r="G45" s="3">
-        <v>11100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>12100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>11200</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>12200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>27200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>16300</v>
-      </c>
-      <c r="O45" s="3">
-        <v>700</v>
       </c>
       <c r="P45" s="3">
         <v>700</v>
       </c>
       <c r="Q45" s="3">
+        <v>700</v>
+      </c>
+      <c r="R45" s="3">
         <v>600</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>469000</v>
+      </c>
+      <c r="E46" s="3">
         <v>493200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>540200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>566900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>580800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>592100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>614100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>625300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>641700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>719700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>745700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>761700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2300</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2687,62 +2792,65 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3">
         <v>416300</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E48" s="3">
         <v>19400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>62900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>65100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>67200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>69200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>71200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>64400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>66900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>68100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>70600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>72000</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2758,47 +2866,50 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6000</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2814,8 +2925,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2870,8 +2984,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2926,37 +3043,40 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>27800</v>
+        <v>13800</v>
       </c>
       <c r="E52" s="3">
         <v>27800</v>
       </c>
       <c r="F52" s="3">
+        <v>27800</v>
+      </c>
+      <c r="G52" s="3">
         <v>20100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>19200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>19400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>600</v>
-      </c>
-      <c r="L52" s="3">
-        <v>300</v>
       </c>
       <c r="M52" s="3">
         <v>300</v>
@@ -2965,25 +3085,28 @@
         <v>300</v>
       </c>
       <c r="O52" s="3">
+        <v>300</v>
+      </c>
+      <c r="P52" s="3">
         <v>416700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>416800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>700</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3038,64 +3161,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>517700</v>
+      </c>
+      <c r="E54" s="3">
         <v>542100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>633100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>654600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>670100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>684000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>694800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>699600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>713900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>793200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>822200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>840100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>417900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>418500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>419300</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3116,8 +3245,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3138,87 +3268,91 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>200</v>
+      </c>
+      <c r="E57" s="3">
         <v>2800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6200</v>
-      </c>
-      <c r="O57" s="3">
-        <v>100</v>
       </c>
       <c r="P57" s="3">
         <v>100</v>
       </c>
       <c r="Q57" s="3">
+        <v>100</v>
+      </c>
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>8300</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3250,143 +3384,152 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>29900</v>
+        <v>6600</v>
       </c>
       <c r="E59" s="3">
-        <v>30600</v>
+        <v>8300</v>
       </c>
       <c r="F59" s="3">
-        <v>33500</v>
+        <v>9300</v>
       </c>
       <c r="G59" s="3">
+        <v>9400</v>
+      </c>
+      <c r="H59" s="3">
+        <v>8300</v>
+      </c>
+      <c r="I59" s="3">
+        <v>7600</v>
+      </c>
+      <c r="J59" s="3">
+        <v>6800</v>
+      </c>
+      <c r="K59" s="3">
+        <v>30100</v>
+      </c>
+      <c r="L59" s="3">
+        <v>28200</v>
+      </c>
+      <c r="M59" s="3">
+        <v>28600</v>
+      </c>
+      <c r="N59" s="3">
         <v>31300</v>
       </c>
-      <c r="H59" s="3">
-        <v>31100</v>
-      </c>
-      <c r="I59" s="3">
-        <v>28200</v>
-      </c>
-      <c r="J59" s="3">
-        <v>30100</v>
-      </c>
-      <c r="K59" s="3">
-        <v>28200</v>
-      </c>
-      <c r="L59" s="3">
-        <v>28600</v>
-      </c>
-      <c r="M59" s="3">
-        <v>31300</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>27300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>200</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>32700</v>
+        <v>26800</v>
       </c>
       <c r="E60" s="3">
         <v>32700</v>
       </c>
       <c r="F60" s="3">
+        <v>32700</v>
+      </c>
+      <c r="G60" s="3">
         <v>35400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>34600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>37100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>34700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>34600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>33900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>34800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>33500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>700</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>34500</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>36700</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>58700</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>60400</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>62000</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>63600</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>65100</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3418,64 +3561,70 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>37000</v>
+        <v>400</v>
       </c>
       <c r="E62" s="3">
-        <v>58900</v>
+        <v>400</v>
       </c>
       <c r="F62" s="3">
-        <v>60600</v>
+        <v>200</v>
       </c>
       <c r="G62" s="3">
-        <v>62300</v>
+        <v>200</v>
       </c>
       <c r="H62" s="3">
-        <v>63900</v>
+        <v>300</v>
       </c>
       <c r="I62" s="3">
-        <v>65100</v>
-      </c>
-      <c r="J62" s="3">
+        <v>300</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>53800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>55800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>57800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>59700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>61600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>24900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>31100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>14600</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3530,8 +3679,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3586,8 +3738,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3642,64 +3797,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>61600</v>
+      </c>
+      <c r="E66" s="3">
         <v>69800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>91600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>96000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>96900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>101000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>98400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>88500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>90500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>91700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>94500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>95100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>26700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>31300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>15300</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3720,8 +3881,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3776,8 +3938,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3832,8 +3997,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3888,8 +4056,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3944,64 +4115,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-852000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-837100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-794300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-766000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-725500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-687400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-652000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-618300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-584800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-550100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-513300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-480300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-25200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-29200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-100</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4056,8 +4233,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4112,8 +4292,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4168,64 +4351,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>456000</v>
+      </c>
+      <c r="E76" s="3">
         <v>472300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>541400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>558600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>573200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>583100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>596400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>611100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>623500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>701500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>727700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>745000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>391200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>387200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>404000</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4280,125 +4469,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-42800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-28300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-40500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-38100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-35400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-33700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-33400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-34700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-36800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-32900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-82400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-13700</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4419,19 +4617,20 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1100</v>
+        <v>1500</v>
       </c>
       <c r="E83" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="F83" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="G83" s="3">
         <v>1500</v>
@@ -4440,43 +4639,46 @@
         <v>1500</v>
       </c>
       <c r="I83" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="J83" s="3">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="K83" s="3">
         <v>1500</v>
       </c>
       <c r="L83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M83" s="3">
         <v>1400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1300</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3">
         <v>1100</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4531,8 +4733,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4587,8 +4792,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4643,8 +4851,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4699,8 +4910,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4755,64 +4969,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-13600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-14900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-18300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-12300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-13700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-19700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-12700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-22600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-49500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-800</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4833,22 +5053,23 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
@@ -4857,40 +5078,43 @@
         <v>-100</v>
       </c>
       <c r="J91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7000</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1900</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4945,8 +5169,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5001,64 +5228,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E94" s="3">
         <v>25500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>35900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>26300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-12400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>28000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>24700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-17000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>110200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-124100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-311500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>266800</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-425300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>9000</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5079,31 +5312,32 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5135,8 +5369,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5191,8 +5428,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5247,8 +5487,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5303,64 +5546,70 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-36900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-12900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-47300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-21500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>218900</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>418800</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5368,107 +5617,113 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H101" s="3">
+        <v>300</v>
+      </c>
+      <c r="I101" s="3">
+        <v>400</v>
+      </c>
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-16700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-25900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>17700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>12600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-35500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>50500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-167800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-313800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>436500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5200</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KIND_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KIND_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
   <si>
     <t>KIND</t>
   </si>
@@ -656,140 +656,143 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>65200</v>
+      </c>
+      <c r="E8" s="3">
         <v>65600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>63300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>53100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>55600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>56100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>56900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>49800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>53300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>54000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>54500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>51000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>192200</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -805,31 +808,34 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E9" s="3">
         <v>11100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10400</v>
-      </c>
-      <c r="J9" s="3">
-        <v>9900</v>
       </c>
       <c r="K9" s="3">
         <v>9900</v>
@@ -838,17 +844,17 @@
         <v>9900</v>
       </c>
       <c r="M9" s="3">
+        <v>9900</v>
+      </c>
+      <c r="N9" s="3">
         <v>10200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>28800</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -864,50 +870,53 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E10" s="3">
         <v>54500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>53000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>43200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>45000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>45400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>46500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>39900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>43400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>44100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>44300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>41900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>163400</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -923,8 +932,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,50 +958,51 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E12" s="3">
         <v>31900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>31100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>31300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>34200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>39600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>37100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>33000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>32000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>33400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>32700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>29000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>97100</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1005,8 +1018,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,13 +1080,16 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>100</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1078,12 +1097,12 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>11100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1099,8 +1118,8 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1123,25 +1142,28 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>600</v>
+      </c>
+      <c r="E15" s="3">
         <v>800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1100</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1400</v>
       </c>
       <c r="G15" s="3">
         <v>1400</v>
       </c>
       <c r="H15" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="I15" s="3">
         <v>1500</v>
@@ -1150,7 +1172,7 @@
         <v>1500</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1182,8 +1204,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,109 +1227,113 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>82300</v>
+      </c>
+      <c r="E17" s="3">
         <v>86400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>112300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>87900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>92100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>100500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>98300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>88600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>89600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>90300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>92800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>84200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>284300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>100</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-20800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-49000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-34700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-36600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-44400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-41400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-38800</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-36300</v>
       </c>
       <c r="L18" s="3">
         <v>-36300</v>
       </c>
       <c r="M18" s="3">
+        <v>-36300</v>
+      </c>
+      <c r="N18" s="3">
         <v>-38300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-33200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-92100</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1320,8 +1349,11 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,50 +1375,51 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
         <v>200</v>
       </c>
       <c r="J20" s="3">
+        <v>200</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>9900</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1402,50 +1435,53 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-19800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-47700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-33500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-35100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-43100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-40200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-37500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-30600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-32900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-35400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-31600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-78100</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1461,8 +1497,11 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1487,8 +1526,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1520,109 +1559,115 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-14700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-42500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-28100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-40500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-37800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-35300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-33400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-32100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-34400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-36800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-32900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-82200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-13700</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1638,8 +1683,11 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,126 +1745,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-14900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-42800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-28300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-40500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-38100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-35400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-33700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-33400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-34700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-36800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-32900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-82400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-13700</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-14900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-42800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-28300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-40500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-38100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-35400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-33700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-33400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-34700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-36800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-32900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-82400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-13700</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,8 +1931,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1933,8 +1993,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2055,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,50 +2117,53 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
         <v>-200</v>
       </c>
       <c r="J32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-9900</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2110,67 +2179,73 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-14900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-42800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-28300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-40500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-38100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-35400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-33700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-33400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-34700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-36800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-32900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-82400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-13700</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2303,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-14900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-42800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-28300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-40500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-38100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-35400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-33700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-33400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-34700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-36800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-32900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-82400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-13700</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2458,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,109 +2482,113 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E41" s="3">
         <v>49700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>53000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>69700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>60200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>48400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>74300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>67800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>55200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>90700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>40200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>208000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>521800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1700</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>381400</v>
+      </c>
+      <c r="E42" s="3">
         <v>375000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>403600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>428100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>470900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>491300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>477300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>507000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>528100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>513700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>626100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>503900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>194000</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2515,50 +2604,53 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E43" s="3">
         <v>29500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>28100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>26100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>26200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>30000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>28400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>28000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>29800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>27000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>26200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>22100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>29700</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2574,8 +2666,11 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2600,8 +2695,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2633,8 +2728,11 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2659,100 +2757,106 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>12200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>27200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>11800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>16300</v>
-      </c>
-      <c r="P45" s="3">
-        <v>700</v>
       </c>
       <c r="Q45" s="3">
         <v>700</v>
       </c>
       <c r="R45" s="3">
+        <v>700</v>
+      </c>
+      <c r="S45" s="3">
         <v>600</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>466700</v>
+      </c>
+      <c r="E46" s="3">
         <v>469000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>493200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>540200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>566900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>580800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>592100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>614100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>625300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>641700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>719700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>745700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>761700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2300</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2777,8 +2881,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2795,65 +2899,68 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R47" s="3">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3">
         <v>416300</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E48" s="3">
         <v>18300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>62900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>65100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>67200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>69200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>71200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>64400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>66900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>68100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>70600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>72000</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2869,8 +2976,11 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2878,41 +2988,41 @@
         <v>1500</v>
       </c>
       <c r="E49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F49" s="3">
         <v>1700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6000</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2928,8 +3038,11 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3100,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,40 +3162,43 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E52" s="3">
         <v>13800</v>
-      </c>
-      <c r="E52" s="3">
-        <v>27800</v>
       </c>
       <c r="F52" s="3">
         <v>27800</v>
       </c>
       <c r="G52" s="3">
-        <v>20100</v>
+        <v>27800</v>
       </c>
       <c r="H52" s="3">
+        <v>12600</v>
+      </c>
+      <c r="I52" s="3">
         <v>19200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>19400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>600</v>
-      </c>
-      <c r="M52" s="3">
-        <v>300</v>
       </c>
       <c r="N52" s="3">
         <v>300</v>
@@ -3088,25 +3207,28 @@
         <v>300</v>
       </c>
       <c r="P52" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q52" s="3">
         <v>416700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>416800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>700</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,67 +3286,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>514000</v>
+      </c>
+      <c r="E54" s="3">
         <v>517700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>542100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>633100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>654600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>670100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>684000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>694800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>699600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>713900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>793200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>822200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>840100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>417900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>418500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>419300</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3374,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,8 +3398,9 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3278,85 +3408,88 @@
         <v>200</v>
       </c>
       <c r="E57" s="3">
+        <v>200</v>
+      </c>
+      <c r="F57" s="3">
         <v>2800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6200</v>
-      </c>
-      <c r="P57" s="3">
-        <v>100</v>
       </c>
       <c r="Q57" s="3">
         <v>100</v>
       </c>
       <c r="R57" s="3">
+        <v>100</v>
+      </c>
+      <c r="S57" s="3">
         <v>500</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E58" s="3">
         <v>8300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5700</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -3387,153 +3520,162 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E59" s="3">
         <v>6600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9300</v>
-      </c>
-      <c r="G59" s="3">
-        <v>9400</v>
       </c>
       <c r="H59" s="3">
         <v>8300</v>
       </c>
       <c r="I59" s="3">
+        <v>8300</v>
+      </c>
+      <c r="J59" s="3">
         <v>7600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>30100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>28200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>28600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>31300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>27300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>200</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E60" s="3">
         <v>26800</v>
-      </c>
-      <c r="E60" s="3">
-        <v>32700</v>
       </c>
       <c r="F60" s="3">
         <v>32700</v>
       </c>
       <c r="G60" s="3">
+        <v>32700</v>
+      </c>
+      <c r="H60" s="3">
         <v>35400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>34600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>37100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>33200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>34700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>34600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>33900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>34800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>33500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>700</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E61" s="3">
         <v>34500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>36700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>58700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>60400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>62000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>63600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>65100</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3564,67 +3706,73 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E62" s="3">
         <v>400</v>
       </c>
       <c r="F62" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G62" s="3">
         <v>200</v>
       </c>
       <c r="H62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I62" s="3">
         <v>300</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="J62" s="3">
+        <v>300</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>53800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>55800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>57800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>59700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>61600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>24900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>31100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>14600</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3830,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3892,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,67 +3954,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>60500</v>
+      </c>
+      <c r="E66" s="3">
         <v>61600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>69800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>91600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>96000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>96900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>101000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>98400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>88500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>90500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>91700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>94500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>95100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>26700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>31300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>15300</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4042,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4102,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4164,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4059,8 +4226,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,67 +4288,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-864100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-852000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-837100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-794300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-766000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-725500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-687400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-652000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-618300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-584800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-550100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-513300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-480300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-25200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-29200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-100</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4412,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4474,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,67 +4536,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>453500</v>
+      </c>
+      <c r="E76" s="3">
         <v>456000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>472300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>541400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>558600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>573200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>583100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>596400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>611100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>623500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>701500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>727700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>745000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>391200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>387200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>404000</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4660,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-14900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-42800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-28300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-40500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-38100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-35400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-33700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-33400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-34700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-36800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-32900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-82400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-13700</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,13 +4815,14 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="E83" s="3">
         <v>1500</v>
@@ -4639,46 +4837,49 @@
         <v>1500</v>
       </c>
       <c r="I83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J83" s="3">
         <v>1400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>1500</v>
       </c>
       <c r="L83" s="3">
         <v>1500</v>
       </c>
       <c r="M83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N83" s="3">
         <v>1400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1300</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3">
         <v>1100</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4937,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +4999,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5061,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5123,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,67 +5185,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-13000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-14900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-18300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-12300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-13700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-19700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-12700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-22600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-49500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-800</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,25 +5273,26 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
@@ -5081,40 +5301,43 @@
         <v>-100</v>
       </c>
       <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7000</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3">
         <v>-1900</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5395,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,67 +5457,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E94" s="3">
         <v>32000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>25500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>35900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>26300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>28000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>24700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-17000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>110200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-124100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-311500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>266800</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-425300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>9000</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,8 +5545,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5339,8 +5572,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5372,8 +5605,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5667,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5729,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,67 +5791,73 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-22300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-36900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-47300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-21500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>218900</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>418800</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5623,107 +5871,113 @@
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R101" s="3">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-16700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>9400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>11800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-25900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>17700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>12600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-35500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>50500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-167800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-313800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>436500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5200</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KIND_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KIND_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
   <si>
     <t>KIND</t>
   </si>
@@ -656,146 +656,150 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>54200</v>
+      </c>
+      <c r="E8" s="3">
         <v>65200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>65600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>63300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>53100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>55600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>56100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>56900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>49800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>53300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>54000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>54500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>51000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>192200</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -811,34 +815,37 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E9" s="3">
         <v>10500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10400</v>
-      </c>
-      <c r="K9" s="3">
-        <v>9900</v>
       </c>
       <c r="L9" s="3">
         <v>9900</v>
@@ -847,17 +854,17 @@
         <v>9900</v>
       </c>
       <c r="N9" s="3">
+        <v>9900</v>
+      </c>
+      <c r="O9" s="3">
         <v>10200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>28800</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -873,53 +880,56 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E10" s="3">
         <v>54800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>54500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>53000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>43200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>45000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>45400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>46500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>39900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>43400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>44100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>44300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>41900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>163400</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -935,8 +945,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,53 +972,54 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E12" s="3">
         <v>33600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>31900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>31100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>31300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>34200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>39600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>37100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>33000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>32000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>33400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>32700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>29000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>97100</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1021,8 +1035,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,29 +1100,32 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>11100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1121,8 +1141,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1145,28 +1165,31 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>500</v>
+      </c>
+      <c r="E15" s="3">
         <v>600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1400</v>
       </c>
       <c r="H15" s="3">
         <v>1400</v>
       </c>
       <c r="I15" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="J15" s="3">
         <v>1500</v>
@@ -1175,7 +1198,7 @@
         <v>1500</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1207,8 +1230,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,115 +1254,119 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>81200</v>
+      </c>
+      <c r="E17" s="3">
         <v>82300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>86400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>112300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>87900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>92100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>100500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>98300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>88600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>89600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>90300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>92800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>84200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>284300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>100</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-17000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-20800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-49000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-34700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-36600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-44400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-41400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-38800</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-36300</v>
       </c>
       <c r="M18" s="3">
         <v>-36300</v>
       </c>
       <c r="N18" s="3">
+        <v>-36300</v>
+      </c>
+      <c r="O18" s="3">
         <v>-38300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-33200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-92100</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1352,8 +1382,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,53 +1409,54 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>200</v>
       </c>
       <c r="K20" s="3">
+        <v>200</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>9900</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1438,53 +1472,56 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-26200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-16800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-19800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-47700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-33500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-35100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-43100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-40200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-37500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-30600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-32900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-35400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-31600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-78100</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1500,8 +1537,11 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1529,8 +1569,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1562,115 +1602,121 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-12100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-42500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-28100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-40500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-37800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-35300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-33400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-32100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-34400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-36800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-32900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-82200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-13700</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1686,8 +1732,11 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,132 +1797,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-14900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-42800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-28300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-40500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-38100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-35400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-33700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-33400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-34700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-36800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-32900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-82400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-13700</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-14900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-42800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-28300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-40500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-38100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-35400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-33700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-33400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-34700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-36800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-32900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-82400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-13700</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,53 +2187,56 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>-200</v>
       </c>
       <c r="K32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2182,70 +2252,76 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-14900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-42800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-28300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-40500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-38100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-35400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-33700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-33400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-34700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-36800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-32900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-82400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-13700</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,137 +2382,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-14900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-42800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-28300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-40500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-38100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-35400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-33700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-33400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-34700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-36800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-32900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-82400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-13700</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,115 +2569,119 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E41" s="3">
         <v>45600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>49700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>53000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>69700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>60200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>48400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>74300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>67800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>55200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>90700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>40200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>208000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>521800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1700</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>360500</v>
+      </c>
+      <c r="E42" s="3">
         <v>381400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>375000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>403600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>428100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>470900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>491300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>477300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>507000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>528100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>513700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>626100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>503900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>194000</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2607,53 +2697,56 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E43" s="3">
         <v>31200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>29500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>28100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>26100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>26200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>30000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>28400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>28000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>29800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>27000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>26200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>22100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>29700</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2669,8 +2762,11 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2698,8 +2794,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2731,8 +2827,11 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2760,103 +2859,109 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>12200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>27200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>16300</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>700</v>
       </c>
       <c r="R45" s="3">
         <v>700</v>
       </c>
       <c r="S45" s="3">
+        <v>700</v>
+      </c>
+      <c r="T45" s="3">
         <v>600</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>451800</v>
+      </c>
+      <c r="E46" s="3">
         <v>466700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>469000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>493200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>540200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>566900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>580800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>592100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>614100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>625300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>641700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>719700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>745700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>761700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2300</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2884,8 +2989,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2902,68 +3007,71 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S47" s="3">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3">
         <v>416300</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E48" s="3">
         <v>17200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>18300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>62900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>65100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>67200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>69200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>71200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>64400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>66900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>68100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>70600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>72000</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2979,53 +3087,56 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="E49" s="3">
         <v>1500</v>
       </c>
       <c r="F49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G49" s="3">
         <v>1700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6000</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3041,8 +3152,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,43 +3282,46 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E52" s="3">
         <v>13600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13800</v>
-      </c>
-      <c r="F52" s="3">
-        <v>27800</v>
       </c>
       <c r="G52" s="3">
         <v>27800</v>
       </c>
       <c r="H52" s="3">
+        <v>27800</v>
+      </c>
+      <c r="I52" s="3">
         <v>12600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>19200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>19400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>600</v>
-      </c>
-      <c r="N52" s="3">
-        <v>300</v>
       </c>
       <c r="O52" s="3">
         <v>300</v>
@@ -3210,25 +3330,28 @@
         <v>300</v>
       </c>
       <c r="Q52" s="3">
+        <v>300</v>
+      </c>
+      <c r="R52" s="3">
         <v>416700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>416800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>700</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,70 +3412,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>495000</v>
+      </c>
+      <c r="E54" s="3">
         <v>514000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>517700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>542100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>633100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>654600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>670100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>684000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>694800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>699600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>713900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>793200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>822200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>840100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>417900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>418500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>419300</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,100 +3529,104 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="E57" s="3">
         <v>200</v>
       </c>
       <c r="F57" s="3">
+        <v>200</v>
+      </c>
+      <c r="G57" s="3">
         <v>2800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6200</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>100</v>
       </c>
       <c r="R57" s="3">
         <v>100</v>
       </c>
       <c r="S57" s="3">
+        <v>100</v>
+      </c>
+      <c r="T57" s="3">
         <v>500</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E58" s="3">
         <v>8500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5700</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -3523,162 +3657,171 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E59" s="3">
         <v>6800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9300</v>
-      </c>
-      <c r="H59" s="3">
-        <v>8300</v>
       </c>
       <c r="I59" s="3">
         <v>8300</v>
       </c>
       <c r="J59" s="3">
+        <v>8300</v>
+      </c>
+      <c r="K59" s="3">
         <v>7600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>30100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>28200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>28600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>31300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>27300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>200</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E60" s="3">
         <v>27900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>26800</v>
-      </c>
-      <c r="F60" s="3">
-        <v>32700</v>
       </c>
       <c r="G60" s="3">
         <v>32700</v>
       </c>
       <c r="H60" s="3">
+        <v>32700</v>
+      </c>
+      <c r="I60" s="3">
         <v>35400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>34600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>37100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>33200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>34700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>34600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>33900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>34800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>33500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>700</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E61" s="3">
         <v>32300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>34500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>36700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>58700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>60400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>62000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>63600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>65100</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3709,8 +3852,11 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3718,61 +3864,64 @@
         <v>300</v>
       </c>
       <c r="E62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F62" s="3">
         <v>400</v>
       </c>
       <c r="G62" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="H62" s="3">
         <v>200</v>
       </c>
       <c r="I62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J62" s="3">
         <v>300</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="K62" s="3">
+        <v>300</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>53800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>55800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>57800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>59700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>61600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>24900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>31100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>14600</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,70 +4112,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E66" s="3">
         <v>60500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>61600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>69800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>91600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>96000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>96900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>101000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>98400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>88500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>90500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>91700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>94500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>95100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>26700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>31300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15300</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4229,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,70 +4462,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-886000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-864100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-852000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-837100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-794300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-766000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-725500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-687400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-652000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-618300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-584800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-550100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-513300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-480300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-25200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-29200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-100</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,70 +4722,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>436100</v>
+      </c>
+      <c r="E76" s="3">
         <v>453500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>456000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>472300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>541400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>558600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>573200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>583100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>596400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>611100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>623500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>701500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>727700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>745000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>391200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>387200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>404000</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,137 +4852,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-14900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-42800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-28300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-40500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-38100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-35400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-33700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-33400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-34700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-36800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-32900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-82400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-13700</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,8 +5014,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4825,7 +5024,7 @@
         <v>1400</v>
       </c>
       <c r="E83" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="F83" s="3">
         <v>1500</v>
@@ -4840,46 +5039,49 @@
         <v>1500</v>
       </c>
       <c r="J83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K83" s="3">
         <v>1400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1300</v>
-      </c>
-      <c r="L83" s="3">
-        <v>1500</v>
       </c>
       <c r="M83" s="3">
         <v>1500</v>
       </c>
       <c r="N83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O83" s="3">
         <v>1400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1300</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3">
         <v>1100</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,70 +5402,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>400</v>
+      </c>
+      <c r="E89" s="3">
         <v>11800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-13000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-14900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-18300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-12300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-19700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-12700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-22600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-49500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-800</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,28 +5494,29 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
@@ -5304,40 +5525,43 @@
         <v>-100</v>
       </c>
       <c r="L91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3">
         <v>-1900</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,70 +5687,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>32000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>25500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>35900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>26300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>28000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>24700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-17000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>110200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-124100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-311500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>266800</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-425300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>9000</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,8 +5779,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5575,8 +5809,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5608,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,75 +6037,81 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-22300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-36900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-12900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-47300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-21500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>218900</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>418800</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
@@ -5874,110 +6123,116 @@
         <v>0</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-16700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>11800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-25900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>17700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>12600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-35500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>50500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-167800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-313800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>436500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5200</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
